--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>24595.6</t>
+          <t>26519.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26803.94</t>
+          <t>26796.8</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>428.23</v>
+        <v>454.28</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>80.34</t>
+          <t>80.13</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>80.99</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23057.2</t>
+          <t>24595.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26874.84</t>
+          <t>26803.94</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
+          <t>-520.2418239468934</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-562.95</v>
+        <v>428.23</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,22 +1608,22 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-45.52</t>
+          <t>-46.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,27 +1891,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>78.75999999999999</t>
+          <t>78.02000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1921,27 +1921,27 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.99</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>82.68</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-75.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-105.98</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19405.2</t>
+          <t>23057.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23022.8</t>
+          <t>23881.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>27026.78</t>
+          <t>26874.84</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3617</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-716.2806444425096</t>
+          <t>-692.691686521878</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-1822.43</v>
+        <v>-562.95</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-46.34</t>
+          <t>-45.52</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>0.91</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-1.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,62 +2307,62 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.75999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>80.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>82.84</t>
+          <t>82.68</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-113.05</t>
+          <t>-75.09</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15481.0</t>
+          <t>16907.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>21269.2</t>
+          <t>19405.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23562.6</t>
+          <t>23022.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28020.06</t>
+          <t>27026.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2293</t>
+          <t>-3617</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-515.1621329656027</t>
+          <t>-716.2806444425096</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-1567.17</v>
+        <v>-1822.43</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-13.36</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>79.0</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>77.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>80.26</t>
+          <t>80.24</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>81.57</t>
+          <t>81.35</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-113.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.82</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18367.0</t>
+          <t>15481.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>25573.8</t>
+          <t>21269.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24025.0</t>
+          <t>23562.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>30101.14</t>
+          <t>28020.06</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>-2293</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-323.8872094882303</t>
+          <t>-515.1621329656027</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-993.76</v>
+        <v>-1567.17</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2901,22 +2901,22 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-45.93</t>
+          <t>-46.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>-1.72</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>79.88000000000001</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>80.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>81.57</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>83.15</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-110.41</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.90</t>
+          <t>-102.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>29056.0</t>
+          <t>18367.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27115.2</t>
+          <t>25573.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>26041.5</t>
+          <t>24025.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>31384.32</t>
+          <t>30101.14</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-202.0915468790305</t>
+          <t>-323.8872094882303</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-448.33</v>
+        <v>-993.76</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-13.36</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-44.28</t>
+          <t>-45.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>79.88000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>83.28</t>
+          <t>83.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.42</t>
+          <t>-110.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.38</t>
+          <t>-101.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>17215.0</t>
+          <t>29056.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24705.4</t>
+          <t>27115.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25479.4</t>
+          <t>26041.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>32291.2</t>
+          <t>31384.32</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-157.3213331716103</t>
+          <t>-202.0915468790305</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-798.37</v>
+        <v>-448.33</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-45.66</t>
+          <t>-44.28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.88</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.28</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.73</t>
+          <t>-14.42</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.33</t>
+          <t>-101.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>26227.0</t>
+          <t>17215.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26640.4</t>
+          <t>24705.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>29789.4</t>
+          <t>25479.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>32293.16</t>
+          <t>32291.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3149</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-40.76661947212246</t>
+          <t>-157.3213331716103</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1.24</v>
+        <v>-798.37</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,42 +4194,42 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>461.0</t>
+          <t>335.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-10.57</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-45.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,32 +4472,32 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>15.87</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>81.42</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4507,27 +4507,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>81.95</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>83.52</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>168.22</t>
+          <t>-29.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.23</t>
+          <t>-101.33</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37004.0</t>
+          <t>26227.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25856.0</t>
+          <t>26640.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31522.8</t>
+          <t>29789.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>32212.7</t>
+          <t>32293.16</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5666</t>
+          <t>-3149</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-47.95254749325315</t>
+          <t>-40.76661947212246</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>171.98</v>
+        <v>-1.24</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,42 +4625,42 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>316.0</t>
+          <t>461.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.52</t>
+          <t>-17.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-43.45</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>81.92</t>
+          <t>81.42</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>80.34</t>
+          <t>80.32</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>81.95</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>83.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>287.76</t>
+          <t>168.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.75</t>
+          <t>-101.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26074.0</t>
+          <t>37004.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22476.2</t>
+          <t>25856.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>29009.3</t>
+          <t>31522.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>32228.3</t>
+          <t>32212.7</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6533</t>
+          <t>-5666</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-87.94094127063738</t>
+          <t>-47.95254749325315</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-741.37</v>
+        <v>171.98</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>316.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.74</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-22.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-43.24</t>
+          <t>-43.45</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>376</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>67.6</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>82.14</t>
+          <t>81.92</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>80.26</t>
+          <t>80.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>82.01</t>
+          <t>81.99</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>83.68</t>
+          <t>83.63</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>193.43</t>
+          <t>287.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.00</t>
+          <t>-101.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>201442.8104196816</t>
+          <t>201212.3735549133</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>17007.0</t>
+          <t>26074.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24967.8</t>
+          <t>22476.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>28410.3</t>
+          <t>29009.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>33728.2</t>
+          <t>32228.3</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3442</t>
+          <t>-6533</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>30.8641925298036</t>
+          <t>-87.94094127063738</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-848.61</v>
+        <v>-741.37</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-8.35</t>
+          <t>-8.69</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-6.378368442726532</t>
+          <t>-10.72059217804787</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-5.228825992056392</t>
+          <t>-7.536483974179959</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>3.352893980248332</t>
+          <t>0.201912828119572</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>49.69</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI2"/>
+  <dimension ref="A1:CI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,42 +878,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>257.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,37 +923,37 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-05 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-20 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-01-06 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-02-03 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -978,43 +978,43 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>257</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,268 +1029,4578 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>79.12</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>80.11</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>81.65</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-71.54</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-114.37</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>18705.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>29034.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>24219.8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>26690.98</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>4814</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-272.6548222598753</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-329.29</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-19.27</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>358.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>14.83</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-49.59</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-3.56</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-4.71</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>79.54</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>80.36</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>81.89</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-79.59</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-111.80</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>26257.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>28674.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>24972.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>27025.76</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-262.3578191087963</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>331.41</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-18.60</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>72.8</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>376.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.34</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-48.83</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-3.31</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-3.92</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>76.74000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>79.88</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>82.11</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-82.91</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-109.45</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>27987.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>26519.6</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>26046.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>26796.8</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-370.3152361963122</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>454.28</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>482.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-4.28</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-4.87</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-47.86</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>8.89</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-2.40</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-3.33</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>77.46</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>80.13</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-80.89</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-107.49</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>36748.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>24595.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>25855.4</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>26803.94</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-1259</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-520.2418239468934</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>428.23</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-15.81</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>458.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-6.34</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-46.83</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>8.89</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-1.18</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-2.89</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>78.02000000000001</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>80.34</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>80.99</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-75.61</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-105.98</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>35475.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>23057.2</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>23881.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>26874.84</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-824</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-692.691686521878</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-562.95</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-14.14</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>79.1</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-8.97</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-15.71</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-45.52</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>26.67</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>8.89</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-1.97</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>78.75999999999999</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>80.34</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>81.19</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>82.68</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-75.09</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-104.85</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>16907.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>19405.2</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>23022.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>27026.78</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-3617</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-716.2806444425096</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-1822.43</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-12.03</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>198.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-7.31</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-9.73</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-46.34</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-1.16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-1.17</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-1.79</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>78.72</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>80.24</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>81.35</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>82.84</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-113.05</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.63</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-103.94</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>15481.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>21269.2</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>23562.6</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>28020.06</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-2293</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-515.1621329656027</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-1567.17</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-13.36</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>5.93</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>14.98</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>7879</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>236.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-7.31</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-46.34</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>79.04</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>80.26</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>81.57</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-130.31</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-102.82</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>18367.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>25573.8</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>24025.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>30101.14</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-323.8872094882303</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-993.76</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-13.36</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>369.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-8.14</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-45.93</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-1.67</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>79.88000000000001</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>80.35</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>81.76</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>83.15</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-110.41</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.30</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-101.90</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>29056.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>27115.2</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>26041.5</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>31384.32</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-202.0915468790305</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-448.33</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-12.69</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>214.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-11.45</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-3.04</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-44.28</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>46.51</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-1.68</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>80.66</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>81.88</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>83.28</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-14.42</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-101.38</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>17215.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>24705.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>25479.4</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>32291.2</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-774</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-157.3213331716103</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-798.37</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-10.02</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>45.43</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>335.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-8.69</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-10.57</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-45.66</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>15.87</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>-2.60</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>80.9</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>80.32</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>81.89</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-29.73</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-101.33</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>200729.6909221902</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>26227.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>26640.4</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>29789.4</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>32293.16</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-3149</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-40.76661947212246</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-12.25</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>5.98</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>7814</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,275 +1009,275 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>200482.5129496403</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>25798.2</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>26711.82</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-739.37</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>5.84</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>15.2</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>48.69</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>7998</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>79.12</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>200729.6909221902</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>29034.4</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>26690.98</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-329.29</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>5.98</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>14.86</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>7814</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>79.12</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.11</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>28674.8</t>
+          <t>29034.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>27025.76</t>
+          <t>26690.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>331.41</v>
+        <v>-329.29</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>79.54</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>26519.6</t>
+          <t>28674.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26796.8</t>
+          <t>27025.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>454.28</v>
+        <v>331.41</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24595.6</t>
+          <t>26519.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26803.94</t>
+          <t>26796.8</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>428.23</v>
+        <v>454.28</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>80.34</t>
+          <t>80.13</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>80.99</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23057.2</t>
+          <t>24595.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26874.84</t>
+          <t>26803.94</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
+          <t>-520.2418239468934</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-562.95</v>
+        <v>428.23</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.97</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-45.52</t>
+          <t>-46.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,27 +3184,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>78.75999999999999</t>
+          <t>78.02000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.99</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>82.68</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-75.61</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-105.98</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19405.2</t>
+          <t>23057.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23022.8</t>
+          <t>23881.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>27026.78</t>
+          <t>26874.84</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3617</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-716.2806444425096</t>
+          <t>-692.691686521878</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1822.43</v>
+        <v>-562.95</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-46.34</t>
+          <t>-45.52</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>0.91</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-1.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,67 +3595,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.75999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>80.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>82.84</t>
+          <t>82.68</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-113.05</t>
+          <t>-75.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15481.0</t>
+          <t>16907.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>21269.2</t>
+          <t>19405.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23562.6</t>
+          <t>23022.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28020.06</t>
+          <t>27026.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2293</t>
+          <t>-3617</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-515.1621329656027</t>
+          <t>-716.2806444425096</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1567.17</v>
+        <v>-1822.43</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-13.36</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>79.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>77.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>80.26</t>
+          <t>80.24</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>81.57</t>
+          <t>81.35</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-113.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.82</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18367.0</t>
+          <t>15481.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>25573.8</t>
+          <t>21269.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24025.0</t>
+          <t>23562.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>30101.14</t>
+          <t>28020.06</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>-2293</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-323.8872094882303</t>
+          <t>-515.1621329656027</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-993.76</v>
+        <v>-1567.17</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.14</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-45.93</t>
+          <t>-46.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>-1.72</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>79.88000000000001</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>80.26</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>81.57</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>83.15</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-110.41</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.90</t>
+          <t>-102.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>29056.0</t>
+          <t>18367.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27115.2</t>
+          <t>25573.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>26041.5</t>
+          <t>24025.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>31384.32</t>
+          <t>30101.14</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-202.0915468790305</t>
+          <t>-323.8872094882303</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-448.33</v>
+        <v>-993.76</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-13.36</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-44.28</t>
+          <t>-45.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>79.88000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>83.28</t>
+          <t>83.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.42</t>
+          <t>-110.41</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.38</t>
+          <t>-101.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>17215.0</t>
+          <t>29056.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24705.4</t>
+          <t>27115.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25479.4</t>
+          <t>26041.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>32291.2</t>
+          <t>31384.32</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-157.3213331716103</t>
+          <t>-202.0915468790305</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-798.37</v>
+        <v>-448.33</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>335.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-8.89</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-10.57</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-45.66</t>
+          <t>-44.28</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,72 +5319,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.87</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>80.32</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.88</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.73</t>
+          <t>-14.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.33</t>
+          <t>-101.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>200729.6909221902</t>
+          <t>200482.5129496403</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26227.0</t>
+          <t>17215.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26640.4</t>
+          <t>24705.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>29789.4</t>
+          <t>25479.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>32293.16</t>
+          <t>32291.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3149</t>
+          <t>-774</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-40.76661947212246</t>
+          <t>-157.3213331716103</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.24</v>
+        <v>-798.37</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-10.02</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.69</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.18</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>25798.2</t>
+          <t>23555.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26711.82</t>
+          <t>26666.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-739.37</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-374.5544038208075</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-540.0904855889603</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>25532</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-17.37</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-19.60</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>73.5</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,288 +1450,293 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>200249.4892241379</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>25798.2</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>26711.82</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>19294</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>47.09</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>79.12</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>200482.5129496403</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>29034.4</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>26690.98</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-329.29</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>5.84</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>7998</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>72.3</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>79.12</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.11</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28674.8</t>
+          <t>29034.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>27025.76</t>
+          <t>26690.98</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>331.41</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-272.6548222598753</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-329.2883395908102</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>18705</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-18.60</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-19.27</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>79.54</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26519.6</t>
+          <t>28674.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26796.8</t>
+          <t>27025.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>454.28</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-262.3578191087963</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>331.4079748725417</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>26257</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-17.37</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-18.60</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>75.5</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>73.1</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24595.6</t>
+          <t>26519.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26803.94</t>
+          <t>26796.8</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>428.23</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-370.3152361963122</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>454.280996431884</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>27987</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-15.81</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>77.1</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>80.34</t>
+          <t>80.13</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>80.99</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23057.2</t>
+          <t>24595.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26874.84</t>
+          <t>26803.94</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-562.95</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-520.2418239468934</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>428.2324202155214</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>36748</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-14.14</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-15.81</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-45.52</t>
+          <t>-46.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,27 +3650,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>78.75999999999999</t>
+          <t>78.02000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3645,27 +3680,27 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.99</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>82.68</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-75.61</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-105.98</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19405.2</t>
+          <t>23057.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23022.8</t>
+          <t>23881.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>27026.78</t>
+          <t>26874.84</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3617</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-716.2806444425096</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-1822.43</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-692.691686521878</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-562.9524179584041</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>35475</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-12.03</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-14.14</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>77.9</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>77.1</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-9.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-46.34</t>
+          <t>-45.52</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>0.91</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-1.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,67 +4066,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.75999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>80.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>82.84</t>
+          <t>82.68</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-113.05</t>
+          <t>-75.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4136,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15481.0</t>
+          <t>16907.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>21269.2</t>
+          <t>19405.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23562.6</t>
+          <t>23022.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28020.06</t>
+          <t>27026.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2293</t>
+          <t>-3617</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-515.1621329656027</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-1567.17</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-716.2806444425096</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-1822.432457565497</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>16907</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-13.36</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-12.03</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>78.9</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>80.26</t>
+          <t>80.24</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>81.57</t>
+          <t>81.35</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.84</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-113.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.82</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18367.0</t>
+          <t>15481.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>25573.8</t>
+          <t>21269.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24025.0</t>
+          <t>23562.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>30101.14</t>
+          <t>28020.06</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>-2293</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-323.8872094882303</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-993.76</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-515.1621329656027</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-1567.174212091151</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>15481</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>-13.36</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>5.84</t>
-        </is>
-      </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
         <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>77.3</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>77.8</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-7.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-45.93</t>
+          <t>-46.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>-1.72</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>79.88000000000001</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>80.26</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>81.57</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>83.15</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-110.41</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.90</t>
+          <t>-102.82</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>29056.0</t>
+          <t>18367.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27115.2</t>
+          <t>25573.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26041.5</t>
+          <t>24025.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>31384.32</t>
+          <t>30101.14</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-202.0915468790305</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-448.33</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-323.8872094882303</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-993.7633538388291</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>18367</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-12.69</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-13.36</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>79.5</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.89</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-44.28</t>
+          <t>-45.93</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>79.88000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>81.88</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>83.28</t>
+          <t>83.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.42</t>
+          <t>-110.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.38</t>
+          <t>-101.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>200482.5129496403</t>
+          <t>200249.4892241379</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>17215.0</t>
+          <t>29056.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24705.4</t>
+          <t>27115.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25479.4</t>
+          <t>26041.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>32291.2</t>
+          <t>31384.32</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-774</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-157.3213331716103</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-798.37</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-202.0915468790305</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-448.3277222698416</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>29056</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-10.02</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-12.69</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>15.2</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>48.69</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>47.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>7782</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>79.8</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>78.4</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>78.18</t>
+          <t>77.62</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23555.0</t>
+          <t>21125.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26666.0</t>
+          <t>26161.88</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>25532</v>
+        <v>15841</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.18</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>25798.2</t>
+          <t>23555.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26711.82</t>
+          <t>26666.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>19294</v>
+        <v>25532</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,280 +1886,280 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>199996.2783357245</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>25798.2</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>26711.82</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>19294</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>14.75</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>47.65</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>7761</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>79.12</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>200249.4892241379</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>29034.4</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>26690.98</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>18705</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>47.09</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>7782</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>79.12</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.11</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>28674.8</t>
+          <t>29034.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>27025.76</t>
+          <t>26690.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>26257</v>
+        <v>18705</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>79.54</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26519.6</t>
+          <t>28674.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>26796.8</t>
+          <t>27025.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>454.280996431884</t>
+          <t>331.4079748725417</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>27987</v>
+        <v>26257</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24595.6</t>
+          <t>26519.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26803.94</t>
+          <t>26796.8</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>428.2324202155214</t>
+          <t>454.280996431884</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>36748</v>
+        <v>27987</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>80.34</t>
+          <t>80.13</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>80.99</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23057.2</t>
+          <t>24595.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26874.84</t>
+          <t>26803.94</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
+          <t>-520.2418239468934</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-562.9524179584041</t>
+          <t>428.2324202155214</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>35475</v>
+        <v>36748</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-7.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-45.52</t>
+          <t>-46.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,27 +4086,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>78.75999999999999</t>
+          <t>78.02000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4116,27 +4116,27 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.99</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>82.68</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-75.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-105.98</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19405.2</t>
+          <t>23057.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23022.8</t>
+          <t>23881.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>27026.78</t>
+          <t>26874.84</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3617</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-716.2806444425096</t>
+          <t>-692.691686521878</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1822.432457565497</t>
+          <t>-562.9524179584041</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>16907</v>
+        <v>35475</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-46.34</t>
+          <t>-45.52</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>0.91</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>-1.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,67 +4502,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.75999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>80.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.84</t>
+          <t>82.68</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-113.05</t>
+          <t>-75.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15481.0</t>
+          <t>16907.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21269.2</t>
+          <t>19405.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23562.6</t>
+          <t>23022.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28020.06</t>
+          <t>27026.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2293</t>
+          <t>-3617</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-515.1621329656027</t>
+          <t>-716.2806444425096</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1567.174212091151</t>
+          <t>-1822.432457565497</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>15481</v>
+        <v>16907</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.36</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>79.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>77.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.76</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>80.26</t>
+          <t>80.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>81.57</t>
+          <t>81.35</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.84</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-113.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.82</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18367.0</t>
+          <t>15481.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>25573.8</t>
+          <t>21269.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24025.0</t>
+          <t>23562.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>30101.14</t>
+          <t>28020.06</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>-2293</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-323.8872094882303</t>
+          <t>-515.1621329656027</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-993.7633538388291</t>
+          <t>-1567.174212091151</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>18367</v>
+        <v>15481</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>236.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-45.93</t>
+          <t>-46.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>-1.61</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>-1.72</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>79.88000000000001</t>
+          <t>79.04</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>80.26</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>81.57</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>83.15</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-110.41</t>
+          <t>-130.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.90</t>
+          <t>-102.82</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>200249.4892241379</t>
+          <t>199996.2783357245</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>29056.0</t>
+          <t>18367.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27115.2</t>
+          <t>25573.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26041.5</t>
+          <t>24025.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>31384.32</t>
+          <t>30101.14</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-202.0915468790305</t>
+          <t>-323.8872094882303</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-448.3277222698416</t>
+          <t>-993.7633538388291</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>29056</v>
+        <v>18367</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-13.36</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.75</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>47.65</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>77.19</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>21125.8</t>
+          <t>18194.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>26161.88</t>
+          <t>25778.86</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>15841</v>
+        <v>11598</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>78.18</t>
+          <t>77.62</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23555.0</t>
+          <t>21125.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26666.0</t>
+          <t>26161.88</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>25532</v>
+        <v>15841</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.18</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>25798.2</t>
+          <t>23555.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26711.82</t>
+          <t>26666.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>19294</v>
+        <v>25532</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,280 +2322,280 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>199734.6747851003</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>25798.2</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>26711.82</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>19294</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>5.92</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>48.44</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>7890</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>79.12</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>199996.2783357245</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>29034.4</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>26690.98</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>18705</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>6.02</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>14.75</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>47.65</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>7761</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>79.12</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28674.8</t>
+          <t>29034.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>27025.76</t>
+          <t>26690.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>26257</v>
+        <v>18705</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>79.54</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26519.6</t>
+          <t>28674.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>26796.8</t>
+          <t>27025.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>454.280996431884</t>
+          <t>331.4079748725417</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>27987</v>
+        <v>26257</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24595.6</t>
+          <t>26519.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26803.94</t>
+          <t>26796.8</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>428.2324202155214</t>
+          <t>454.280996431884</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>36748</v>
+        <v>27987</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.08</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>80.34</t>
+          <t>80.13</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>80.99</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23057.2</t>
+          <t>24595.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>26874.84</t>
+          <t>26803.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
+          <t>-520.2418239468934</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-562.9524179584041</t>
+          <t>428.2324202155214</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>35475</v>
+        <v>36748</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-45.52</t>
+          <t>-46.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,27 +4522,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>78.75999999999999</t>
+          <t>78.02000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,27 +4552,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.99</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.68</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-75.61</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-105.98</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19405.2</t>
+          <t>23057.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23022.8</t>
+          <t>23881.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>27026.78</t>
+          <t>26874.84</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3617</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-716.2806444425096</t>
+          <t>-692.691686521878</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1822.432457565497</t>
+          <t>-562.9524179584041</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>16907</v>
+        <v>35475</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-46.34</t>
+          <t>-45.52</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>0.91</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>-1.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,67 +4938,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.75999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>80.34</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>82.84</t>
+          <t>82.68</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-113.05</t>
+          <t>-75.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15481.0</t>
+          <t>16907.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21269.2</t>
+          <t>19405.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23562.6</t>
+          <t>23022.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28020.06</t>
+          <t>27026.78</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2293</t>
+          <t>-3617</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-515.1621329656027</t>
+          <t>-716.2806444425096</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1567.174212091151</t>
+          <t>-1822.432457565497</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>15481</v>
+        <v>16907</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.36</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>79.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>77.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>236.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>79.04</t>
+          <t>78.72</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>80.26</t>
+          <t>80.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>81.57</t>
+          <t>81.35</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-130.31</t>
+          <t>-113.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.82</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>199996.2783357245</t>
+          <t>199734.6747851003</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18367.0</t>
+          <t>15481.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>25573.8</t>
+          <t>21269.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24025.0</t>
+          <t>23562.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>30101.14</t>
+          <t>28020.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>-2293</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-323.8872094882303</t>
+          <t>-515.1621329656027</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-993.7633538388291</t>
+          <t>-1567.174212091151</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>18367</v>
+        <v>15481</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>14.75</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>48.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>77.19</t>
+          <t>76.99</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>79.08</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18194.0</t>
+          <t>22036.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>25778.86</t>
+          <t>25490.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>11598</v>
+        <v>37918</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>77.62</t>
+          <t>77.19</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>21125.8</t>
+          <t>18194.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>26161.88</t>
+          <t>25778.86</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>15841</v>
+        <v>11598</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>78.18</t>
+          <t>77.62</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23555.0</t>
+          <t>21125.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>26666.0</t>
+          <t>26161.88</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>25532</v>
+        <v>15841</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.18</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>25798.2</t>
+          <t>23555.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>26711.82</t>
+          <t>26666.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>19294</v>
+        <v>25532</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,280 +2758,280 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>79.9</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/17</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>199530.3004291845</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>25798.2</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>26711.82</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>19294</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>15.86</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>49.24</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>8343</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>79.12</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>199734.6747851003</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>29034.4</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>26690.98</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>18705</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>5.92</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>79.54</t>
+          <t>79.12</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.11</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28674.8</t>
+          <t>29034.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>27025.76</t>
+          <t>26690.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>26257</v>
+        <v>18705</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>79.88</t>
+          <t>79.54</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26519.6</t>
+          <t>28674.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26796.8</t>
+          <t>27025.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>454.280996431884</t>
+          <t>331.4079748725417</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>27987</v>
+        <v>26257</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>79.88</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24595.6</t>
+          <t>26519.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>26803.94</t>
+          <t>26796.8</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>428.2324202155214</t>
+          <t>454.280996431884</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>36748</v>
+        <v>27987</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>80.34</t>
+          <t>80.13</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>80.99</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>23057.2</t>
+          <t>24595.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>26874.84</t>
+          <t>26803.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
+          <t>-520.2418239468934</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-562.9524179584041</t>
+          <t>428.2324202155214</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>35475</v>
+        <v>36748</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-45.52</t>
+          <t>-46.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,17 +4938,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4958,27 +4958,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>78.75999999999999</t>
+          <t>78.02000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4988,27 +4988,27 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.99</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>82.68</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-75.61</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-105.98</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19405.2</t>
+          <t>23057.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23022.8</t>
+          <t>23881.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>27026.78</t>
+          <t>26874.84</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3617</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-716.2806444425096</t>
+          <t>-692.691686521878</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1822.432457565497</t>
+          <t>-562.9524179584041</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>16907</v>
+        <v>35475</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>198.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-15.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-46.34</t>
+          <t>-45.52</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>0.91</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>-1.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,67 +5374,67 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>78.72</t>
+          <t>78.75999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>80.24</t>
+          <t>80.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>82.84</t>
+          <t>82.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-113.05</t>
+          <t>-75.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>199734.6747851003</t>
+          <t>199530.3004291845</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15481.0</t>
+          <t>16907.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21269.2</t>
+          <t>19405.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23562.6</t>
+          <t>23022.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28020.06</t>
+          <t>27026.78</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2293</t>
+          <t>-3617</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-515.1621329656027</t>
+          <t>-716.2806444425096</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1567.174212091151</t>
+          <t>-1822.432457565497</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>15481</v>
+        <v>16907</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.36</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>49.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>77.9</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>79.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>77.5</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>77.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>73.8</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>76.99</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>79.08</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>79.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>37918.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>22036.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>22036.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>25535.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>25490.96</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>25490.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-271.2655854032491</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>37918</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>37918.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>72.82000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>77.19</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>79.18</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>79.18000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>11598.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>18194.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>18194</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>23434.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>25778.86</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>25778.86</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1805.975277406487</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>11598</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>11598.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>72.8</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>77.62</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>79.4</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>77.62</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>79.40000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>15841.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>21125.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>21125.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>23822.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>26161.88</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>26161.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1113.918577503737</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>15841</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>15841.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>73.24000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>78.18</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>79.63</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>79.63</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>25532.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>23555.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>23555</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>24075.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>26666.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>26666</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-540.0904855889603</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>25532</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>25532.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>73.91999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>78.7</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>79.9</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>79.90000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>19294.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>25798.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>25798.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>24427.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>26711.82</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>26711.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-739.3685512253905</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>19294</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>79.12</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>80.11</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>18705.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>29034.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>29034.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>24219.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>26690.98</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>26690.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-329.2883395908102</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>18705</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>18705.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>75.8</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>79.54</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>80.36</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>80.36</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>26257.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>28674.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>28674.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>24972.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>27025.76</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>27025.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>331.4079748725417</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>26257</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>26257.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>76.74000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>79.88</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>80.6</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>27987.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>26519.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>26519.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>26046.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>26796.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>26796.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>454.280996431884</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>27987</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>27987.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>77.46</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>80.13</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>80.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>36748.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>24595.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>24595.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>25855.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>26803.94</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>26803.94</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>428.2324202155214</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>36748</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>36748.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>78.02000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>80.34</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>80.99</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>80.98999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>35475.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>23057.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>23057.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>23881.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>26874.84</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>26874.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-562.9524179584041</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>35475</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>35475.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>78.75999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>80.34</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>81.19</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>81.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>16907.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>19405.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>19405.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>23022.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>27026.78</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>27026.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-1822.432457565497</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>16907</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>16907.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN4" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>78.7</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>79.90000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>25798.2</v>
+        <v>23555</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26711.82</v>
+        <v>26666</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,274 +3164,274 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>199359.8571428571</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>25798.2</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>26711.82</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>5.66</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>49.59</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>8256</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM7" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/17</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>199530.3004291845</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>29034.4</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>26690.98</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>15.86</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>49.24</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>8343</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>79.54000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>80.36</v>
+        <v>80.11</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>28674.8</v>
+        <v>29034.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>27025.76</v>
+        <v>26690.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>79.88</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>80.59999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>26519.6</v>
+        <v>28674.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26796.8</v>
+        <v>27025.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>454.280996431884</t>
+          <t>331.4079748725417</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>80.13</v>
+        <v>79.88</v>
       </c>
       <c r="AN10" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>24595.6</v>
+        <v>26519.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26803.94</v>
+        <v>26796.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>428.2324202155214</t>
+          <t>454.280996431884</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>80.34</v>
+        <v>80.13</v>
       </c>
       <c r="AN11" t="n">
-        <v>80.98999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>23057.2</v>
+        <v>24595.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26874.84</v>
+        <v>26803.94</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
+          <t>-520.2418239468934</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-562.9524179584041</t>
+          <t>428.2324202155214</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>458.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.71</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-45.52</t>
+          <t>-46.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>692</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>78.75999999999999</t>
+          <t>78.02000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>80.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>81.19</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>82.68</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-75.09</t>
+          <t>-75.61</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.85</t>
+          <t>-105.98</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/17</t>
+          <t>2025/11/27</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>199530.3004291845</t>
+          <t>199359.8571428571</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>19405.2</v>
+        <v>23057.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23022.8</t>
+          <t>23881.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>27026.78</v>
+        <v>26874.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3617</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-716.2806444425096</t>
+          <t>-692.691686521878</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1822.432457565497</t>
+          <t>-562.9524179584041</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>16907.0</t>
+          <t>35475.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.24</t>
+          <t>49.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN3" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN6" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>78.7</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>79.90000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>25798.2</v>
+        <v>23555</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26711.82</v>
+        <v>26666</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,274 +3594,274 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>199109.0456490728</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>25798.2</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>26711.82</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>15.84</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>8332</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM8" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>199359.8571428571</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>29034.4</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>26690.98</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>5.66</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>15.7</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>49.59</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>8256</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>79.54000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>80.36</v>
+        <v>80.11</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>28674.8</v>
+        <v>29034.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>27025.76</v>
+        <v>26690.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>79.88</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>80.59999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>26519.6</v>
+        <v>28674.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26796.8</v>
+        <v>27025.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>454.280996431884</t>
+          <t>331.4079748725417</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>80.13</v>
+        <v>79.88</v>
       </c>
       <c r="AN11" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>24595.6</v>
+        <v>26519.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26803.94</v>
+        <v>26796.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>428.2324202155214</t>
+          <t>454.280996431884</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>458.0</t>
+          <t>482.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-46.83</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>204</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-3.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>78.02000000000001</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>80.34</v>
+        <v>80.13</v>
       </c>
       <c r="AN12" t="n">
-        <v>80.98999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-75.61</t>
+          <t>-80.89</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.98</t>
+          <t>-107.49</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>199359.8571428571</t>
+          <t>199109.0456490728</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>23057.2</v>
+        <v>24595.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23881.3</t>
+          <t>25855.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26874.84</v>
+        <v>26803.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-824</t>
+          <t>-1259</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-692.691686521878</t>
+          <t>-520.2418239468934</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-562.9524179584041</t>
+          <t>428.2324202155214</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>35475.0</t>
+          <t>36748.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.84</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN4" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>78.7</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>79.90000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>25798.2</v>
+        <v>23555</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26711.82</v>
+        <v>26666</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,274 +4024,274 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>198877.844017094</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>25798.2</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>26711.82</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>15.49</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>49.44</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>8149</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM9" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>199109.0456490728</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>29034.4</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>26690.98</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>15.84</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>8332</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>79.54000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>80.36</v>
+        <v>80.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>28674.8</v>
+        <v>29034.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>27025.76</v>
+        <v>26690.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>79.88</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>80.59999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>26519.6</v>
+        <v>28674.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26796.8</v>
+        <v>27025.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>454.280996431884</t>
+          <t>331.4079748725417</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>482.0</t>
+          <t>376.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>76.74000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>80.13</v>
+        <v>79.88</v>
       </c>
       <c r="AN12" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.11</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-80.89</t>
+          <t>-82.91</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-107.49</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>199109.0456490728</t>
+          <t>198877.844017094</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>24595.6</v>
+        <v>26519.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25855.4</t>
+          <t>26046.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26803.94</v>
+        <v>26796.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1259</t>
+          <t>472</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-520.2418239468934</t>
+          <t>-370.3152361963122</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>428.2324202155214</t>
+          <t>454.280996431884</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36748.0</t>
+          <t>27987.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-17.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.44</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN5" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN7" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>78.7</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>79.90000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>25798.2</v>
+        <v>23555</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26711.82</v>
+        <v>26666</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,274 +4454,274 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>198635.1379800854</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>25798.2</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>26711.82</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>15.35</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>49.06</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>8073</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM10" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>198877.844017094</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>29034.4</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>26690.98</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>5.73</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>49.44</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>8149</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>79.54000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>80.36</v>
+        <v>80.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>28674.8</v>
+        <v>29034.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>27025.76</v>
+        <v>26690.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>376.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-49.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>76.74000000000001</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>79.88</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>80.59999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>82.11</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-82.91</t>
+          <t>-79.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-109.45</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>198877.844017094</t>
+          <t>198635.1379800854</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>26519.6</v>
+        <v>28674.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26046.7</t>
+          <t>24972.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26796.8</v>
+        <v>27025.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-370.3152361963122</t>
+          <t>-262.3578191087963</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>454.280996431884</t>
+          <t>331.4079748725417</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>27987.0</t>
+          <t>26257.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.35</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>49.06</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN6" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN7" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN8" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN9" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>78.7</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>79.90000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>25798.2</v>
+        <v>23555</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26711.82</v>
+        <v>26666</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,274 +4884,274 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>198373.9261363636</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>25798.2</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>26711.82</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>49.61</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM11" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>198635.1379800854</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>29034.4</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>26690.98</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>15.35</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>49.06</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>8073</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>257.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>19.88</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-49.59</t>
+          <t>-50.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>79.54000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>80.36</v>
+        <v>80.11</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>81.65</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-79.59</t>
+          <t>-71.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>198635.1379800854</t>
+          <t>198373.9261363636</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>28674.8</v>
+        <v>29034.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24972.0</t>
+          <t>24219.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>27025.76</v>
+        <v>26690.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-262.3578191087963</t>
+          <t>-272.6548222598753</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>331.4079748725417</t>
+          <t>-329.2883395908102</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>26257.0</t>
+          <t>18705.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-19.27</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.35</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.06</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN6" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN7" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.66</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN8" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.70</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>78.7</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>79.90000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-52.66</t>
+          <t>-47.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>198373.9261363636</t>
+          <t>198146.9872340425</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>25798.2</v>
+        <v>23555</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26711.82</v>
+        <v>26666</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.53</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.61</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>257.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19.88</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-50.00</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,274 +5314,274 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.84</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>-1.88</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>73.91999999999999</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>81.43</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-52.66</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-1.24</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>-1.88</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-116.54</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>198146.9872340425</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>25798.2</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>24427.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>26711.82</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-344.4569344084161</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-739.3685512253905</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>19294.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-17.37</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>5.67</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>15.66</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>49.79</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>8236</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>73.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="AM12" t="n">
-        <v>79.12</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>80.11</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>81.65</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-71.54</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-114.37</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>198373.9261363636</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>29034.4</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>24219.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>26690.98</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-272.6548222598753</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-329.2883395908102</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>18705.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-19.27</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>15.53</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>49.61</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>73.1</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,274 +1014,266 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.52</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
+          <t>72.84</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.4</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>197905.183427762</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>15.57</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>50.05</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>8193</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>198146.9872340425</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>5.67</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>49.79</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>8236</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>63.58</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+          <t>68.52</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.59</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>23.00</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
+          <t>28.78</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.27</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.84</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
+          <t>63.58</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.35</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.16</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-1.44</t>
-        </is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.36</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>83.33</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-0.55</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
+          <t>72.84</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.57</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21.63</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.18</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
+          <t>19.74</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-1.44</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2591,11 +2559,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>3088</t>
@@ -2603,12 +2567,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2592,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2612,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2667,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2677,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2698,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.44</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.53</t>
-        </is>
+          <t>83.33</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.17</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.98</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
+          <t>21.63</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1.51</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2766,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2776,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2832,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2877,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2902,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2917,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2942,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3021,11 +2977,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>3088</t>
@@ -3033,12 +2985,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3000,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3010,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3030,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3085,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3095,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3116,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>69.57</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-3.18</t>
-        </is>
+          <t>94.44</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.53</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN7" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.54</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1.59</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3184,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3194,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3250,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3295,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3305,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3320,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3335,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3360,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3451,11 +3395,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>3088</t>
@@ -3463,12 +3403,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3418,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3428,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3448,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3503,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3513,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3534,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>41.18</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.14</t>
-        </is>
+          <t>69.57</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-3.18</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN8" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.33</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
+          <t>7.65</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1.67</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3602,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3612,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3668,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3713,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3738,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3753,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3778,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3825,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3840,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3850,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3870,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3925,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3935,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3956,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.84</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-5.66</t>
-        </is>
+          <t>41.18</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-4.14</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.08</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
+          <t>-5.33</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1.7</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4024,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4034,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4090,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4135,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4160,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4175,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4200,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4247,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4262,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4272,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4292,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4347,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4357,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4378,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-1.10</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-6.22</t>
-        </is>
+          <t>7.84</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-5.66</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN10" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-40.47</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-2.19</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.56</t>
-        </is>
+          <t>-29.08</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.68</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4446,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4456,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4512,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4567,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4582,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4597,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4622,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4669,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4684,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4694,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4714,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4769,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4779,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4800,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4902,56 +4818,48 @@
           <t>8.72</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-6.32</t>
-        </is>
+      <c r="AH11" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-6.22</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN11" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-47.09</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-2.06</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-1.40</t>
-        </is>
+          <t>-40.47</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.56</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4868,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4878,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4934,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +4989,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5004,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5019,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5044,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5091,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>351.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5106,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5116,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5136,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5191,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-50.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5201,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5222,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5240,48 @@
           <t>8.72</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-6.07</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-6.32</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.91999999999999</t>
+          <t>73.24000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>78.7</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>79.90000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>81.43</t>
+          <t>81.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-52.66</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.89</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-1.24</t>
-        </is>
+          <t>-47.09</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-1.4</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5290,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.54</t>
+          <t>-118.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5300,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>198146.9872340425</t>
+          <t>197905.183427762</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>25798.2</v>
+        <v>23555</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24427.7</t>
+          <t>24075.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26711.82</v>
+        <v>26666</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>-520</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-344.4569344084161</t>
+          <t>-374.5544038208075</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-739.3685512253905</t>
+          <t>-540.0904855889603</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>19294.0</t>
+          <t>25532.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5356,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.37</t>
+          <t>-19.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5401,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5411,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5426,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>15.57</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5441,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5471,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,266 +1436,266 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>197664.2376237624</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>15.45</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>49.87</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>8128</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>197905.183427762</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>15.57</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>50.05</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>8193</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.91</v>
+        <v>-0.32</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2559,7 +2559,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>3088</t>
@@ -2567,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2582,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2592,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2677,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2698,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.55</v>
+        <v>-1.91</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.51</v>
+        <v>-1.44</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2776,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2832,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2877,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2902,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2917,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2942,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2977,7 +2981,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>3088</t>
@@ -2985,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3000,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3010,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3085,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3095,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3116,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.66</v>
+        <v>-0.55</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.53</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.27</v>
+        <v>-1.18</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3184,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3194,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3250,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3295,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3320,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3335,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3360,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3395,7 +3403,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>3088</t>
@@ -3403,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3428,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3503,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3513,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3534,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.18</v>
+        <v>-1.53</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN8" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.54</v>
+        <v>-1.27</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3612,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3668,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3723,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3753,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3778,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3815,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3825,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3840,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3935,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3956,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>4.88</v>
+        <v>3.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.14</v>
+        <v>-3.18</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN9" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.79</v>
+        <v>-1.54</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.7</v>
+        <v>-1.67</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4034,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4090,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4135,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4160,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4175,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4200,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4247,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4262,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4272,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4347,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4357,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4378,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.52</v>
+        <v>4.88</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5.66</v>
+        <v>-4.14</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-2.17</v>
+        <v>-1.79</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.68</v>
+        <v>-1.7</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4456,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4512,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4557,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4582,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4597,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4622,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4669,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4684,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4694,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4769,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4779,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4800,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-1.1</v>
+        <v>0.52</v>
       </c>
       <c r="AI11" t="n">
-        <v>-6.22</v>
+        <v>-5.66</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.19</v>
+        <v>-2.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.56</v>
+        <v>-1.68</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4868,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4878,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4934,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4989,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5004,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5019,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5044,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5091,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>351.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5106,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5116,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-11.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5191,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-50.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5201,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5222,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5241,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.42</v>
+        <v>-1.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.32</v>
+        <v>-6.22</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.24000000000001</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>78.18000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="AN12" t="n">
-        <v>79.63</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>81.19</t>
+          <t>80.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-47.09</t>
+          <t>-40.47</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.06</v>
+        <v>-2.19</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.4</v>
+        <v>-1.56</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.75</t>
+          <t>-120.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5300,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>197905.183427762</t>
+          <t>197664.2376237624</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>23555</v>
+        <v>21125.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>24075.3</t>
+          <t>23822.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26666</v>
+        <v>26161.88</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-520</t>
+          <t>-2696</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-374.5544038208075</t>
+          <t>-488.3027382335658</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-540.0904855889603</t>
+          <t>-1113.918577503737</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>25532.0</t>
+          <t>15841.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5356,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-19.60</t>
+          <t>-19.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5411,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5426,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.57</t>
+          <t>15.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5441,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>49.87</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5466,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>72.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>72.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-48.00</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.31999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.15</t>
+          <t>80.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.71</t>
+          <t>-113.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>18182.6</v>
+        <v>18465.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>23414.0</t>
+          <t>24279.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25364.22</v>
+        <v>25229.94</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5231</t>
+          <t>-5813</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-582.8117649193613</t>
+          <t>-669.2429782178583</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1233.875796507586</t>
+          <t>-1144.614651359592</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,266 +1858,266 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>197427.9576271186</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>5.73</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>15.49</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>49.86</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>197664.2376237624</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>15.45</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>49.87</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>8128</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.91</v>
+        <v>-0.32</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AN6" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.55</v>
+        <v>-1.91</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.51</v>
+        <v>-1.44</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.66</v>
+        <v>-0.55</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.53</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN8" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.27</v>
+        <v>-1.18</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.18</v>
+        <v>-1.53</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN9" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.54</v>
+        <v>-1.27</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>4.88</v>
+        <v>3.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.14</v>
+        <v>-3.18</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN10" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.79</v>
+        <v>-1.54</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.7</v>
+        <v>-1.67</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.52</v>
+        <v>4.88</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.66</v>
+        <v>-4.14</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.17</v>
+        <v>-1.79</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.68</v>
+        <v>-1.7</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.32</t>
+          <t>-22.36</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-50.34</t>
+          <t>-49.52</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.1</v>
+        <v>0.52</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.22</v>
+        <v>-5.66</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>72.82000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>77.62</v>
+        <v>77.19</v>
       </c>
       <c r="AN12" t="n">
-        <v>79.40000000000001</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>80.96</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-40.47</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.19</v>
+        <v>-2.17</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.56</v>
+        <v>-1.68</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.86</t>
+          <t>-122.50</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>197664.2376237624</t>
+          <t>197427.9576271186</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>21125.8</v>
+        <v>18194</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23822.7</t>
+          <t>23434.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>26161.88</v>
+        <v>25778.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2696</t>
+          <t>-5240</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-488.3027382335658</t>
+          <t>-691.0215904140152</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1113.918577503737</t>
+          <t>-1805.975277406487</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>15841.0</t>
+          <t>11598.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-19.82</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-11.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-47.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,33 +1014,33 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1050,30 +1050,30 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.82000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.2</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AN2" t="n">
-        <v>78.06999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.72</t>
+          <t>-112.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>18465.6</v>
+        <v>19333.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>24279.4</t>
+          <t>21904.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>25229.94</v>
+        <v>24862.94</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5813</t>
+          <t>-2570</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-669.2429782178583</t>
+          <t>-798.5504405646504</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1144.614651359592</t>
+          <t>-1509.741483472008</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-48.00</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>75.31999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.15</t>
+          <t>80.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.71</t>
+          <t>-113.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>18182.6</v>
+        <v>18465.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23414.0</t>
+          <t>24279.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25364.22</v>
+        <v>25229.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5231</t>
+          <t>-5813</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-582.8117649193613</t>
+          <t>-669.2429782178583</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1233.875796507586</t>
+          <t>-1144.614651359592</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,266 +2280,266 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>197179.4746121297</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>15.51</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>49.76</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>8161</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>197427.9576271186</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>5.73</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>15.49</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>8150</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AN6" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.91</v>
+        <v>-0.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AN7" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.55</v>
+        <v>-1.91</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.51</v>
+        <v>-1.44</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.66</v>
+        <v>-0.55</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.53</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.27</v>
+        <v>-1.18</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.18</v>
+        <v>-1.53</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN10" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.54</v>
+        <v>-1.27</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>4.88</v>
+        <v>3.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.14</v>
+        <v>-3.18</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN11" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.79</v>
+        <v>-1.54</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.7</v>
+        <v>-1.67</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-49.52</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>187</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.52</v>
+        <v>4.88</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.66</v>
+        <v>-4.14</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>72.82000000000001</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>77.19</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>79.18000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>80.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.17</v>
+        <v>-1.79</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.68</v>
+        <v>-1.7</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.50</t>
+          <t>-122.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>197427.9576271186</t>
+          <t>197179.4746121297</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18194</v>
+        <v>22036.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23434.4</t>
+          <t>25535.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>25778.86</v>
+        <v>25490.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5240</t>
+          <t>-3498</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-691.0215904140152</t>
+          <t>-626.443743489282</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1805.975277406487</t>
+          <t>-271.2655854032491</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>11598.0</t>
+          <t>37918.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.79</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.82000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.04000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>77.97</v>
+        <v>77.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.92</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.67</v>
+        <v>-0.61</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.96</v>
+        <v>-0.89</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.78</t>
+          <t>-111.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>19333.8</v>
+        <v>17076</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>21904.5</t>
+          <t>17986.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>24862.94</v>
+        <v>23968.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2570</t>
+          <t>-910</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-798.5504405646504</t>
+          <t>-939.9791003029957</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1509.741483472008</t>
+          <t>-1717.836728863895</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-11.74</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-47.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,33 +1436,33 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1472,30 +1472,30 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.82000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>75.2</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>78.06999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.72</t>
+          <t>-112.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>18465.6</v>
+        <v>19333.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>24279.4</t>
+          <t>21904.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>25229.94</v>
+        <v>24862.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5813</t>
+          <t>-2570</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-669.2429782178583</t>
+          <t>-798.5504405646504</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1144.614651359592</t>
+          <t>-1509.741483472008</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-48.00</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>75.31999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>80.15</t>
+          <t>80.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.71</t>
+          <t>-113.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>18182.6</v>
+        <v>18465.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23414.0</t>
+          <t>24279.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>25364.22</v>
+        <v>25229.94</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5231</t>
+          <t>-5813</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-582.8117649193613</t>
+          <t>-669.2429782178583</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1233.875796507586</t>
+          <t>-1144.614651359592</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,266 +2702,266 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>196931.9661971831</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>5.72</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>15.53</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>49.63</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>197179.4746121297</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>49.76</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>8161</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.91</v>
+        <v>-0.32</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AN8" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.55</v>
+        <v>-1.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AN9" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1.51</v>
+        <v>-1.44</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.66</v>
+        <v>-0.55</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.53</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.27</v>
+        <v>-1.18</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>692.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-47.17</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>69.57</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.18</v>
+        <v>-1.53</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>76.72</v>
+        <v>76.47</v>
       </c>
       <c r="AN11" t="n">
-        <v>78.95999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>80.57</t>
+          <t>80.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-1.54</v>
+        <v>-1.27</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.67</v>
+        <v>-1.59</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.38</t>
+          <t>-121.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>28873.8</v>
+        <v>26906.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27336.0</t>
+          <t>25230.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>26087.8</v>
+        <v>25739.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-225.9196539318388</t>
+          <t>-88.49375878934178</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1976.962838634099</t>
+          <t>667.3486644943914</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>53480.0</t>
+          <t>15694.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.70</t>
+          <t>-13.92</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>500.0</t>
+          <t>692.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>188</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>69.57</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>4.88</v>
+        <v>3.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>-4.14</v>
+        <v>-3.18</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.28</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>76.98999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="AN12" t="n">
-        <v>79.08</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>80.66</t>
+          <t>80.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.79</v>
+        <v>-1.54</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.7</v>
+        <v>-1.67</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.80</t>
+          <t>-122.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>197179.4746121297</t>
+          <t>196931.9661971831</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>22036.6</v>
+        <v>28873.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25535.5</t>
+          <t>27336.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>25490.96</v>
+        <v>26087.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-3498</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-626.443743489282</t>
+          <t>-225.9196539318388</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-271.2655854032491</t>
+          <t>1976.962838634099</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>37918.0</t>
+          <t>53480.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>15.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -923,79 +923,79 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-11.68</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-10.95</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-02-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,12 +1094,12 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1109,51 +1109,51 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>75.85999999999999</t>
+          <t>76.26</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>75.04000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>77.84999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.48</v>
+        <v>-0.32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-110.79</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>15584.2</v>
+        <v>14380.4</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>17500.0</t>
+          <t>16281.5</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>23969.02</v>
+        <v>23885.46</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-1915</t>
+          <t>-1901</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-1115.479620628169</t>
+          <t>-1277.496786353545</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-2080.732482416621</t>
+          <t>-2168.591197843112</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,33 +1556,33 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>0.13</v>
+        <v>1.24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1592,30 +1592,30 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.85999999999999</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>74.97</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>77.92</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>79.92</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.61</v>
+        <v>-0.48</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.89</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-111.87</t>
+          <t>-110.79</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>17076</v>
+        <v>15584.2</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>17986.4</t>
+          <t>17500.0</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>23968.32</v>
+        <v>23969.02</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-910</t>
+          <t>-1915</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-939.9791003029957</t>
+          <t>-1115.479620628169</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-1717.836728863895</t>
+          <t>-2080.732482416621</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
           <t>76.8</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>75.8</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.79</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>75.82000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>75.04000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="AV4" t="n">
-        <v>77.97</v>
+        <v>77.92</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.92</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.67</v>
+        <v>-0.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.96</v>
+        <v>-0.89</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-112.78</t>
+          <t>-111.87</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>19333.8</v>
+        <v>17076</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>21904.5</t>
+          <t>17986.4</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>24862.94</v>
+        <v>23968.32</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-2570</t>
+          <t>-910</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-798.5504405646504</t>
+          <t>-939.9791003029957</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-1509.741483472008</t>
+          <t>-1717.836728863895</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-11.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-47.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,33 +2480,33 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2516,30 +2516,30 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.82000000000001</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>75.2</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>78.06999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-113.72</t>
+          <t>-112.78</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>18465.6</v>
+        <v>19333.8</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>24279.4</t>
+          <t>21904.5</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>25229.94</v>
+        <v>24862.94</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-5813</t>
+          <t>-2570</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-669.2429782178583</t>
+          <t>-798.5504405646504</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-1144.614651359592</t>
+          <t>-1509.741483472008</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-48.00</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>75.31999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>80.15</t>
+          <t>80.09</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-114.71</t>
+          <t>-113.72</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>18182.6</v>
+        <v>18465.6</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>23414.0</t>
+          <t>24279.4</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>25364.22</v>
+        <v>25229.94</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-5231</t>
+          <t>-5813</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-582.8117649193613</t>
+          <t>-669.2429782178583</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-1233.875796507586</t>
+          <t>-1144.614651359592</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,266 +3866,266 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>196427.625</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BF8" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="BH8" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>15.86</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>50.14</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>8344</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>196677.835443038</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BF8" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="BH8" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>15.74</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>49.92</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>8279</t>
-        </is>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CJ8" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CL8" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CM8" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CN8" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CO8" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AV9" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-1.91</v>
+        <v>-0.32</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AV10" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-0.55</v>
+        <v>-1.91</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AV11" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-1.51</v>
+        <v>-1.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>15.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-46.69</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>2.66</v>
+        <v>-0.55</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-1.53</v>
+        <v>-0.17</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.02000000000001</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>76.47</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AV12" t="n">
-        <v>78.90000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>80.44</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>21.63</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-1.27</v>
+        <v>-1.18</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-121.31</t>
+          <t>-120.22</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>196677.835443038</t>
+          <t>196427.625</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>26906.2</v>
+        <v>28645.4</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>25230.6</t>
+          <t>24885.6</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>25739.18</v>
+        <v>25877.18</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-88.49375878934178</t>
+          <t>-13.77779190109874</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>667.3486644943914</t>
+          <t>397.160025984238</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>15694.0</t>
+          <t>24537.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-13.92</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>50.14</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>86.67</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>1.49</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>1.42</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-3.34</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-2.49</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>76.26</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>75.2</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>79.78</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>54.38</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.71</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-109.49</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>12352.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>14380.4</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>16281.5</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>23885.46</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-1901</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-1277.496786353545</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-2168.591197843112</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>12352.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-13.81</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>76.7</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>77.4</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>76.3</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>77.4</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>64.44</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>1.1</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-3.62</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-2.50</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>75.85999999999999</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>75.04000000000001</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>77.84999999999999</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>79.85</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>40.26</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.48</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-110.79</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>10830.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>15584.2</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>17500.0</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>23969.02</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-1915</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-1115.479620628169</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-2080.732482416621</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>10830.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-14.48</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>75.9</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>76.9</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>75.9</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>76.8</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-1.05</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>40.83</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>0.13</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>0.97</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-3.78</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-2.50</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>75.7</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>74.97</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>77.92</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>79.92</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>30.69</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.61</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-111.87</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>14299.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>17076</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>17986.4</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>23968.32</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-910</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-939.9791003029957</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-1717.836728863895</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>14299.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-15.59</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>76.4</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>76.8</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>75.8</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-1.32</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>33.33</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>27.5</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-0.16</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>1.04</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-3.76</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-2.53</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>75.82000000000001</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>75.04000000000001</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>77.97</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>29.41</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.67</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.96</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-112.78</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>14169.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>19333.8</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>21904.5</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>24862.94</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-2570</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-798.5504405646504</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-1509.741483472008</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>14169.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-15.70</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>76.1</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>76.8</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>75.7</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-0.93</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>38.61</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>0.84</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-3.67</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-2.53</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>75.84</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>75.2</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>78.06999999999999</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>80.09</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>28.79</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.73</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-1.03</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-113.72</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>20252.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>18465.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>24279.4</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>25229.94</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-5813</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-669.2429782178583</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-1144.614651359592</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>20252.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-15.81</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>76.5</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>75.4</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>-1.46</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>20.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>56.05</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-0.4</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>0.51</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-3.66</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-2.46</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>75.7</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>75.31999999999999</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>78.17</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>80.15</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>28.97</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.78</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-1.1</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-114.71</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>18371.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>18182.6</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>23414.0</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>25364.22</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-5231</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-582.8117649193613</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-1233.875796507586</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>18371.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-16.04</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>76.1</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>76.7</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>75.4</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-1.18</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>72.84</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>0.34</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>0.4</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-3.65</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.39</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>75.74000000000001</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>75.44</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>78.29000000000001</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>80.21</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>30.99</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-1.18</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-115.77</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>18289.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>19415.8</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>23161.0</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>25512.84</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-3745</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-464.436486448775</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-1115.789011129447</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>18289.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-15.37</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>77.0</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>77.3</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>76.0</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-1.57</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>81.48</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>68.52</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.53</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>0.59</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-3.64</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-2.29</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>76.0</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>75.55</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>78.41</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>80.25</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>28.78</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-1.27</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-117.00</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>25588.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>18896.8</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>23885.3</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>25717.76</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-4988</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-346.0087546886527</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-898.4582816203438</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>25588.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-14.92</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.68</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>76.5</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>77.6</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>76.4</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>76.4</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.13</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>70.37</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>63.58</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>0.35</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-3.5</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.21</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>76.03999999999999</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>75.78</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>78.52</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>80.3</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>23.00</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-1.05</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-1.36</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-118.22</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>9828.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>24475.2</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>23255.9</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>25624.6</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-245.5633861556179</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-1337.933729406617</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>9828.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-15.59</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>75.5</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>76.2</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>75.5</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>75.8</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-2.00</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>72.84</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-1.91</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>0.57</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-3.46</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-2.13</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>76.35999999999999</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>75.92</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>78.65000000000001</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>80.36</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>19.74</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-1.16</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-1.44</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-119.27</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>18837.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>30093.2</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>24143.6</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>25752.2</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>5949</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-46.95059647361804</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-229.4010216224742</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>18837.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-16.59</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>76.5</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>76.5</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>74.8</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>74.9</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/03/25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>126.0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2024/07/31</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/05</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.91</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-0.55</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-3.34</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-2.06</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>76.02000000000001</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>76.15000000000001</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>78.78</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>80.44</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>21.63</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-1.18</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-1.51</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-120.22</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>196427.625</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>24537.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>28645.4</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>24885.6</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>25877.18</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>3759</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-13.77779190109874</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>397.160025984238</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>24537.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-15.81</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>0.201912828119572</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>16.21</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>15.86</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>33.70%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>10.52%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>50.14</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>8344</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>艾訊-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>77.7</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>77.8</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>45.43</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 工業電腦、其他電腦及週邊設備** 觸控面板 - 資訊收集設備、工業用設備</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AT2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AU2" t="n">
         <v>1.49</v>
       </c>
-      <c r="AU2" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>76.26</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>75.2</v>
+        <v>75.38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>77.79000000000001</v>
+        <v>77.73</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.71</v>
+        <v>-0.62</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-108.25</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>12352.0</t>
+          <t>18786.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>14380.4</v>
+        <v>14087.2</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>16281.5</t>
+          <t>16276.4</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>23885.46</v>
+        <v>23893.84</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-1901</t>
+          <t>-2189</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1277.496786353545</t>
+          <t>-1341.470745175396</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-2168.591197843112</t>
+          <t>-1693.32751869558</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>12352.0</t>
+          <t>18786.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,79 +1425,79 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-11.68</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-10.95</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-02-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,12 +1616,12 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1631,51 +1631,51 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>75.85999999999999</t>
+          <t>76.26</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>75.04000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>77.84999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.48</v>
+        <v>-0.32</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-110.79</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>15584.2</v>
+        <v>14380.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>17500.0</t>
+          <t>16281.5</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>23969.02</v>
+        <v>23885.46</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-1915</t>
+          <t>-1901</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1115.479620628169</t>
+          <t>-1277.496786353545</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2080.732482416621</t>
+          <t>-2168.591197843112</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,33 +2098,33 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.13</v>
+        <v>1.24</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -2134,30 +2134,30 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.85999999999999</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>74.97</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>77.92</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>79.92</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.61</v>
+        <v>-0.48</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.89</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-111.87</t>
+          <t>-110.79</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>17076</v>
+        <v>15584.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>17986.4</t>
+          <t>17500.0</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>23968.32</v>
+        <v>23969.02</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-910</t>
+          <t>-1915</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-939.9791003029957</t>
+          <t>-1115.479620628169</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1717.836728863895</t>
+          <t>-2080.732482416621</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
           <t>76.8</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>75.8</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.79</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>75.82000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>75.04000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="AZ5" t="n">
-        <v>77.97</v>
+        <v>77.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.92</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.67</v>
+        <v>-0.61</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.96</v>
+        <v>-0.89</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-112.78</t>
+          <t>-111.87</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>19333.8</v>
+        <v>17076</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>21904.5</t>
+          <t>17986.4</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>24862.94</v>
+        <v>23968.32</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-2570</t>
+          <t>-910</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-798.5504405646504</t>
+          <t>-939.9791003029957</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1509.741483472008</t>
+          <t>-1717.836728863895</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-11.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-47.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,33 +3062,33 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -3098,30 +3098,30 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.82000000000001</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>75.2</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>78.06999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-113.72</t>
+          <t>-112.78</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>18465.6</v>
+        <v>19333.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>24279.4</t>
+          <t>21904.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>25229.94</v>
+        <v>24862.94</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-5813</t>
+          <t>-2570</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-669.2429782178583</t>
+          <t>-798.5504405646504</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1144.614651359592</t>
+          <t>-1509.741483472008</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-48.00</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>75.31999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>80.15</t>
+          <t>80.09</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-114.71</t>
+          <t>-113.72</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>18182.6</v>
+        <v>18465.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>23414.0</t>
+          <t>24279.4</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>25364.22</v>
+        <v>25229.94</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-5231</t>
+          <t>-5813</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-582.8117649193613</t>
+          <t>-669.2429782178583</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1233.875796507586</t>
+          <t>-1144.614651359592</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,266 +4508,266 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AY9" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>196191.652173913</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BJ9" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="BL9" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>15.74</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>49.37</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>8279</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>196427.625</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BJ9" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="BL9" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>15.86</t>
-        </is>
-      </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>50.14</t>
-        </is>
-      </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>8344</t>
-        </is>
-      </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CO9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-1.91</v>
+        <v>-0.32</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AZ11" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.11</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-48.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.55</v>
+        <v>-1.91</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.17</v>
+        <v>0.57</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>76.02000000000001</t>
+          <t>76.35999999999999</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>76.15000000000001</v>
+        <v>75.92</v>
       </c>
       <c r="AZ12" t="n">
-        <v>78.78</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>80.44</t>
+          <t>80.36</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.18</v>
+        <v>-1.16</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.51</v>
+        <v>-1.44</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-120.22</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>196427.625</t>
+          <t>196191.652173913</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>28645.4</v>
+        <v>30093.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>24885.6</t>
+          <t>24143.6</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>25877.18</v>
+        <v>25752.2</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-13.77779190109874</t>
+          <t>-46.95059647361804</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>397.160025984238</t>
+          <t>-229.4010216224742</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>24537.0</t>
+          <t>18837.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>49.37</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1153,47 +1153,47 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.84</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>75.38</v>
+        <v>75.62</v>
       </c>
       <c r="AZ2" t="n">
-        <v>77.73</v>
+        <v>77.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>79.67</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>60.39</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.62</v>
+        <v>-0.52</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-108.25</t>
+          <t>-106.95</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>18786.0</t>
+          <t>17597.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>14087.2</v>
+        <v>14772.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>16276.4</t>
+          <t>17053.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>23893.84</v>
+        <v>23744.84</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2189</t>
+          <t>-2280</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1341.470745175396</t>
+          <t>-1351.626746736861</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1693.32751869558</t>
+          <t>-1407.484755324916</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>18786.0</t>
+          <t>17597.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,34 +1425,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>247.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>77.4</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AT3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AU3" t="n">
         <v>1.49</v>
       </c>
-      <c r="AU3" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>76.26</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>75.2</v>
+        <v>75.38</v>
       </c>
       <c r="AZ3" t="n">
-        <v>77.79000000000001</v>
+        <v>77.73</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.71</v>
+        <v>-0.62</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-108.25</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>12352.0</t>
+          <t>18786.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>14380.4</v>
+        <v>14087.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>16281.5</t>
+          <t>16276.4</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>23885.46</v>
+        <v>23893.84</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-1901</t>
+          <t>-2189</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1277.496786353545</t>
+          <t>-1341.470745175396</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2168.591197843112</t>
+          <t>-1693.32751869558</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>12352.0</t>
+          <t>18786.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,79 +1907,79 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-11.68</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-10.95</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-02-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,12 +2098,12 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>75.85999999999999</t>
+          <t>76.26</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>75.04000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>77.84999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.48</v>
+        <v>-0.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-110.79</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>15584.2</v>
+        <v>14380.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>17500.0</t>
+          <t>16281.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>23969.02</v>
+        <v>23885.46</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-1915</t>
+          <t>-1901</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1115.479620628169</t>
+          <t>-1277.496786353545</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2080.732482416621</t>
+          <t>-2168.591197843112</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,33 +2580,33 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.13</v>
+        <v>1.24</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -2616,30 +2616,30 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.85999999999999</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>74.97</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>77.92</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>79.92</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.61</v>
+        <v>-0.48</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.89</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-111.87</t>
+          <t>-110.79</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>17076</v>
+        <v>15584.2</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>17986.4</t>
+          <t>17500.0</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>23968.32</v>
+        <v>23969.02</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-910</t>
+          <t>-1915</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-939.9791003029957</t>
+          <t>-1115.479620628169</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1717.836728863895</t>
+          <t>-2080.732482416621</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
           <t>76.8</t>
-        </is>
-      </c>
-      <c r="CR5" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
-      </c>
-      <c r="CS5" t="inlineStr">
-        <is>
-          <t>75.8</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.79</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>75.82000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>75.04000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="AZ6" t="n">
-        <v>77.97</v>
+        <v>77.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.92</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.67</v>
+        <v>-0.61</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.96</v>
+        <v>-0.89</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-112.78</t>
+          <t>-111.87</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>19333.8</v>
+        <v>17076</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>21904.5</t>
+          <t>17986.4</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>24862.94</v>
+        <v>23968.32</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-2570</t>
+          <t>-910</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-798.5504405646504</t>
+          <t>-939.9791003029957</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1509.741483472008</t>
+          <t>-1717.836728863895</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-11.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-47.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,33 +3544,33 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -3580,30 +3580,30 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.82000000000001</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>75.2</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>78.06999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-113.72</t>
+          <t>-112.78</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>18465.6</v>
+        <v>19333.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>24279.4</t>
+          <t>21904.5</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>25229.94</v>
+        <v>24862.94</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-5813</t>
+          <t>-2570</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-669.2429782178583</t>
+          <t>-798.5504405646504</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1144.614651359592</t>
+          <t>-1509.741483472008</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CR7" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-48.00</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>75.31999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>80.15</t>
+          <t>80.09</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-114.71</t>
+          <t>-113.72</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>18182.6</v>
+        <v>18465.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>23414.0</t>
+          <t>24279.4</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>25364.22</v>
+        <v>25229.94</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-5231</t>
+          <t>-5813</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-582.8117649193613</t>
+          <t>-669.2429782178583</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1233.875796507586</t>
+          <t>-1144.614651359592</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,266 +4990,266 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AY10" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>195953.8424369748</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BJ10" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="BL10" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>15.86</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>49.56</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>8344</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AY10" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>196191.652173913</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BJ10" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="BL10" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>15.74</t>
-        </is>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="CK10" t="inlineStr">
-        <is>
-          <t>49.37</t>
-        </is>
-      </c>
-      <c r="CL10" t="inlineStr">
-        <is>
-          <t>8279</t>
-        </is>
-      </c>
-      <c r="CM10" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN10" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CO10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CP10" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CQ10" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AZ11" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="BD11" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-48.34</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>70.37</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-1.91</v>
+        <v>-0.32</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>76.35999999999999</t>
+          <t>76.03999999999999</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>75.92</v>
+        <v>75.78</v>
       </c>
       <c r="AZ12" t="n">
-        <v>78.65000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>80.36</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.16</v>
+        <v>-1.05</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-118.22</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>196191.652173913</t>
+          <t>195953.8424369748</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>30093.2</v>
+        <v>24475.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>24143.6</t>
+          <t>23255.9</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>25752.2</v>
+        <v>25624.6</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-46.95059647361804</t>
+          <t>-245.5633861556179</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-229.4010216224742</t>
+          <t>-1337.933729406617</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>18837.0</t>
+          <t>9828.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>49.37</t>
+          <t>49.56</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>228.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>-10.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.73</v>
+        <v>-0.62</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>76.84</t>
+          <t>76.97999999999999</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>75.62</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>77.7</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>79.67</t>
+          <t>79.61</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>74.19</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.52</v>
+        <v>-0.44</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-106.95</t>
+          <t>-105.86</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>17597.0</t>
+          <t>9873.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>14772.8</v>
+        <v>13887.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>17053.3</t>
+          <t>15481.8</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>23744.84</v>
+        <v>23571.44</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2280</t>
+          <t>-1594</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1351.626746736861</t>
+          <t>-1413.146893713086</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1407.484755324916</t>
+          <t>-1751.507702082328</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>17597.0</t>
+          <t>9873.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>247.0</t>
+          <t>228.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.45</t>
+          <t>-13.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,17 +1616,17 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1635,47 +1635,47 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.84</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>75.38</v>
+        <v>75.62</v>
       </c>
       <c r="AZ3" t="n">
-        <v>77.73</v>
+        <v>77.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>79.72</t>
+          <t>79.67</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>60.39</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.62</v>
+        <v>-0.52</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-108.25</t>
+          <t>-106.95</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>18786.0</t>
+          <t>17597.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>14087.2</v>
+        <v>14772.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>16276.4</t>
+          <t>17053.3</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>23893.84</v>
+        <v>23744.84</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-2189</t>
+          <t>-2280</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-1341.470745175396</t>
+          <t>-1351.626746736861</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1693.32751869558</t>
+          <t>-1407.484755324916</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>18786.0</t>
+          <t>17597.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>247.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-13.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-46.62</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AT4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AU4" t="n">
         <v>1.49</v>
       </c>
-      <c r="AU4" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>76.26</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>75.2</v>
+        <v>75.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>77.79000000000001</v>
+        <v>77.73</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>79.72</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>60.39</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.32</v>
+        <v>-0.24</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.71</v>
+        <v>-0.62</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-108.25</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>12352.0</t>
+          <t>18786.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>14380.4</v>
+        <v>14087.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>16281.5</t>
+          <t>16276.4</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>23885.46</v>
+        <v>23893.84</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-1901</t>
+          <t>-2189</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-1277.496786353545</t>
+          <t>-1341.470745175396</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-2168.591197843112</t>
+          <t>-1693.32751869558</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>12352.0</t>
+          <t>18786.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,79 +2389,79 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.18</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-11.68</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-02-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-02-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-02-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>141.0</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-10.95</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-02-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-02-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-02-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-46.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>75.85999999999999</t>
+          <t>76.26</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>75.04000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>77.84999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>79.85</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>54.38</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.48</v>
+        <v>-0.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-110.79</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>15584.2</v>
+        <v>14380.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>17500.0</t>
+          <t>16281.5</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>23969.02</v>
+        <v>23885.46</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-1915</t>
+          <t>-1901</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-1115.479620628169</t>
+          <t>-1277.496786353545</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2080.732482416621</t>
+          <t>-2168.591197843112</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>10830.0</t>
+          <t>12352.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,33 +3062,33 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>40.83</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.13</v>
+        <v>1.24</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -3098,30 +3098,30 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.85999999999999</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>74.97</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>77.92</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>79.92</t>
+          <t>79.85</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.61</v>
+        <v>-0.48</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.89</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-111.87</t>
+          <t>-110.79</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>17076</v>
+        <v>15584.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>17986.4</t>
+          <t>17500.0</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>23968.32</v>
+        <v>23969.02</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-910</t>
+          <t>-1915</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-939.9791003029957</t>
+          <t>-1115.479620628169</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1717.836728863895</t>
+          <t>-2080.732482416621</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>14299.0</t>
+          <t>10830.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>75.9</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
           <t>76.8</t>
-        </is>
-      </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>75.6</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>75.8</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.74</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-47.79</t>
+          <t>-47.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>40.83</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-3.76</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>75.82000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>75.04000000000001</v>
+        <v>74.97</v>
       </c>
       <c r="AZ7" t="n">
-        <v>77.97</v>
+        <v>77.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.92</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.67</v>
+        <v>-0.61</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.96</v>
+        <v>-0.89</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-112.78</t>
+          <t>-111.87</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>19333.8</v>
+        <v>17076</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>21904.5</t>
+          <t>17986.4</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>24862.94</v>
+        <v>23968.32</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-2570</t>
+          <t>-910</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-798.5504405646504</t>
+          <t>-939.9791003029957</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1509.741483472008</t>
+          <t>-1717.836728863895</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>14169.0</t>
+          <t>14299.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-15.59</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>267.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-23.95</t>
+          <t>-11.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-47.86</t>
+          <t>-47.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,33 +4026,33 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>29.17</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>38.61</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -4062,30 +4062,30 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>75.82000000000001</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>75.2</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>78.06999999999999</v>
+        <v>77.97</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.73</v>
+        <v>-0.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-113.72</t>
+          <t>-112.78</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>18465.6</v>
+        <v>19333.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>24279.4</t>
+          <t>21904.5</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>25229.94</v>
+        <v>24862.94</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-5813</t>
+          <t>-2570</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-669.2429782178583</t>
+          <t>-798.5504405646504</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1144.614651359592</t>
+          <t>-1509.741483472008</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>20252.0</t>
+          <t>14169.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-15.81</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
           <t>75.6</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>75.4</t>
-        </is>
-      </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>243.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-23.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-48.00</t>
+          <t>-47.86</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>38.61</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>75.31999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>78.17</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>80.15</t>
+          <t>80.09</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.1</v>
+        <v>-1.03</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-114.71</t>
+          <t>-113.72</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>18182.6</v>
+        <v>18465.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>23414.0</t>
+          <t>24279.4</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>25364.22</v>
+        <v>25229.94</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-5231</t>
+          <t>-5813</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-582.8117649193613</t>
+          <t>-669.2429782178583</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1233.875796507586</t>
+          <t>-1144.614651359592</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>18371.0</t>
+          <t>20252.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-15.81</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.17</t>
+          <t>-22.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-47.59</t>
+          <t>-48.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>56.05</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>75.74000000000001</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>75.44</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>78.29000000000001</v>
+        <v>78.17</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>80.21</t>
+          <t>80.15</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>28.97</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="BD10" t="n">
-        <v>-1.18</v>
+        <v>-1.1</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.71</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>19415.8</v>
+        <v>18182.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>23161.0</t>
+          <t>23414.0</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>25512.84</v>
+        <v>25364.22</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-3745</t>
+          <t>-5231</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-464.436486448775</t>
+          <t>-582.8117649193613</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1115.789011129447</t>
+          <t>-1233.875796507586</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>18289.0</t>
+          <t>18371.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-15.37</t>
+          <t>-16.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>332.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-16.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-47.31</t>
+          <t>-47.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,266 +5472,266 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>75.74000000000001</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>80.21</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>7.47</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>-115.77</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/11/27</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>195700.4937062937</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BJ11" t="n">
+        <v>19415.8</v>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>23161.0</t>
+        </is>
+      </c>
+      <c r="BL11" t="n">
+        <v>25512.84</v>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-3745</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-464.436486448775</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-1115.789011129447</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>18289.0</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2024/09/27</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>-15.37</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>艾訊</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>-10.72059217804787</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>-7.536483974179959</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>0.201912828119572</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>5.66</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>16.21</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>15.68</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>33.70%</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>10.52%</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>49.39</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>艾訊-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
           <t>76.0</t>
-        </is>
-      </c>
-      <c r="AY11" t="n">
-        <v>75.55</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>80.25</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>28.78</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>7.47</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>-117.00</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/11/27</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>195953.8424369748</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BJ11" t="n">
-        <v>18896.8</v>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>23885.3</t>
-        </is>
-      </c>
-      <c r="BL11" t="n">
-        <v>25717.76</v>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-4988</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-346.0087546886527</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-898.4582816203438</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>25588.0</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>89.8</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2024/09/27</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-14.92</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>艾訊</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>-10.72059217804787</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>-7.536483974179959</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0.201912828119572</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>15.86</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>33.70%</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>10.52%</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>49.56</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>8344</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>智能物聯網產品42.60%、智能設計服務產品32.46%、博奕產品13.05%、其他11.89% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>艾訊-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>76.5</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>77.6</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>76.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>332.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>-20.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-47.72</t>
+          <t>-47.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>70.37</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>68.52</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.32</v>
+        <v>0.53</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.35</v>
+        <v>0.59</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>76.03999999999999</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>75.78</v>
+        <v>75.55</v>
       </c>
       <c r="AZ12" t="n">
-        <v>78.52</v>
+        <v>78.41</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>23.00</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="BD12" t="n">
-        <v>-1.36</v>
+        <v>-1.27</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-118.22</t>
+          <t>-117.00</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>195953.8424369748</t>
+          <t>195700.4937062937</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>24475.2</v>
+        <v>18896.8</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>23255.9</t>
+          <t>23885.3</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>25624.6</v>
+        <v>25717.76</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-4988</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-245.5633861556179</t>
+          <t>-346.0087546886527</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-1337.933729406617</t>
+          <t>-898.4582816203438</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>9828.0</t>
+          <t>25588.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-15.59</t>
+          <t>-14.92</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>49.39</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/資訊收集設備.xlsx
+++ b/Result/checksun_type/資訊收集設備.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV12"/>
+  <dimension ref="A1:CW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,320 +611,325 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross_d</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -943,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.30</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-47.24</t>
+          <t>-46.69</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,300 +1118,305 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-03-13 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>-0.62</v>
+          <t>94.44</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>83.15</t>
+        </is>
       </c>
       <c r="AU2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
+        <v>0.29</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.43</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>76.97999999999999</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>75.73999999999999</v>
+          <t>-2.40</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>77.08000000000001</t>
+        </is>
       </c>
       <c r="AZ2" t="n">
-        <v>77.65000000000001</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>79.61</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>77.61</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>74.19</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.11</v>
+          <t>79.52</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>90.55</t>
+        </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+        <v>-0.03</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-105.86</t>
-        </is>
-      </c>
       <c r="BG2" t="inlineStr">
         <is>
+          <t>-104.78</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
           <t>2025/11/27</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>195700.4937062937</t>
-        </is>
-      </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>9873.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>13887.6</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>15481.8</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>23571.44</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-1594</t>
-        </is>
+          <t>195446.9224860335</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>9429.0</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>13607.4</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>14595.8</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>23471.92</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-1413.146893713086</t>
+          <t>-988</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1751.507702082328</t>
+          <t>-1500.637536566528</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>9873.0</t>
+          <t>-1981.836072260458</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9429.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>2024/09/27</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>-14.81</t>
-        </is>
-      </c>
       <c r="BU2" t="inlineStr">
         <is>
+          <t>-13.92</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>艾訊</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-10.72059217804787</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-7.536483974179959</t>
         </is